--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_VELABASKET CB SUECA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_VELABASKET CB SUECA.xlsx
@@ -565,13 +565,13 @@
         <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>129.2941</v>
+        <v>106.1206</v>
       </c>
       <c r="E2" t="n">
-        <v>98.0792</v>
+        <v>82.04769999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>31.215</v>
+        <v>24.0731</v>
       </c>
       <c r="G2" t="n">
         <v>52.2876</v>
@@ -610,13 +610,13 @@
         <v>55.2891</v>
       </c>
       <c r="S2" t="n">
-        <v>42.5574</v>
+        <v>19.3837</v>
       </c>
       <c r="T2" t="n">
-        <v>24.4087</v>
+        <v>8.3772</v>
       </c>
       <c r="U2" t="n">
-        <v>18.1488</v>
+        <v>11.0064</v>
       </c>
       <c r="V2" t="n">
         <v>35.0151</v>
@@ -643,13 +643,13 @@
         <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>60.9792</v>
+        <v>83.4395</v>
       </c>
       <c r="E3" t="n">
-        <v>55.7533</v>
+        <v>71.8736</v>
       </c>
       <c r="F3" t="n">
-        <v>5.2262</v>
+        <v>11.566</v>
       </c>
       <c r="G3" t="n">
         <v>37.5038</v>
@@ -688,13 +688,13 @@
         <v>45.288</v>
       </c>
       <c r="S3" t="n">
-        <v>-20.6941</v>
+        <v>1.7664</v>
       </c>
       <c r="T3" t="n">
-        <v>-17.6415</v>
+        <v>-1.5211</v>
       </c>
       <c r="U3" t="n">
-        <v>-3.0527</v>
+        <v>3.2879</v>
       </c>
       <c r="V3" t="n">
         <v>22.2802</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. CERVANTES GUERRA</t>
+          <t>E. MORATA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>46.6495</v>
+        <v>50.0967</v>
       </c>
       <c r="E4" t="n">
-        <v>31.8575</v>
+        <v>40.3305</v>
       </c>
       <c r="F4" t="n">
-        <v>14.7916</v>
+        <v>9.766300000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>18.2256</v>
+        <v>20.0359</v>
       </c>
       <c r="H4" t="n">
-        <v>12.3015</v>
+        <v>16.3861</v>
       </c>
       <c r="I4" t="n">
-        <v>5.9239</v>
+        <v>3.650300000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>42.2705</v>
+        <v>50.4553</v>
       </c>
       <c r="K4" t="n">
-        <v>31.8503</v>
+        <v>40.1027</v>
       </c>
       <c r="L4" t="n">
-        <v>10.4202</v>
+        <v>10.3527</v>
       </c>
       <c r="M4" t="n">
-        <v>-24.0451</v>
+        <v>-30.4197</v>
       </c>
       <c r="N4" t="n">
-        <v>-19.5486</v>
+        <v>-23.7169</v>
       </c>
       <c r="O4" t="n">
-        <v>-4.4965</v>
+        <v>-6.7026</v>
       </c>
       <c r="P4" t="n">
-        <v>13.9638</v>
+        <v>17.3604</v>
       </c>
       <c r="Q4" t="n">
-        <v>-24.1536</v>
+        <v>-31.7016</v>
       </c>
       <c r="R4" t="n">
-        <v>38.1174</v>
+        <v>49.062</v>
       </c>
       <c r="S4" t="n">
-        <v>15.9661</v>
+        <v>6.4906</v>
       </c>
       <c r="T4" t="n">
-        <v>7.7613</v>
+        <v>3.4282</v>
       </c>
       <c r="U4" t="n">
-        <v>8.204800000000001</v>
+        <v>3.0621</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.5061</v>
+        <v>6.2099</v>
       </c>
       <c r="W4" t="n">
-        <v>5.979000000000001</v>
+        <v>18.1482</v>
       </c>
       <c r="X4" t="n">
-        <v>-7.4851</v>
+        <v>-11.9383</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. MORATA</t>
+          <t>L. CERVANTES GUERRA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
-        <v>41.5462</v>
+        <v>40.81</v>
       </c>
       <c r="E5" t="n">
-        <v>36.0975</v>
+        <v>27.5954</v>
       </c>
       <c r="F5" t="n">
-        <v>5.4491</v>
+        <v>13.2144</v>
       </c>
       <c r="G5" t="n">
-        <v>20.0359</v>
+        <v>18.2256</v>
       </c>
       <c r="H5" t="n">
-        <v>16.3861</v>
+        <v>12.3015</v>
       </c>
       <c r="I5" t="n">
-        <v>3.650300000000001</v>
+        <v>5.9239</v>
       </c>
       <c r="J5" t="n">
-        <v>50.4553</v>
+        <v>42.2705</v>
       </c>
       <c r="K5" t="n">
-        <v>40.1027</v>
+        <v>31.8503</v>
       </c>
       <c r="L5" t="n">
-        <v>10.3527</v>
+        <v>10.4202</v>
       </c>
       <c r="M5" t="n">
-        <v>-30.4197</v>
+        <v>-24.0451</v>
       </c>
       <c r="N5" t="n">
-        <v>-23.7169</v>
+        <v>-19.5486</v>
       </c>
       <c r="O5" t="n">
-        <v>-6.7026</v>
+        <v>-4.4965</v>
       </c>
       <c r="P5" t="n">
-        <v>17.3604</v>
+        <v>13.9638</v>
       </c>
       <c r="Q5" t="n">
-        <v>-31.7016</v>
+        <v>-24.1536</v>
       </c>
       <c r="R5" t="n">
-        <v>49.062</v>
+        <v>38.1174</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.0598</v>
+        <v>10.1267</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8050999999999999</v>
+        <v>3.499</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.2549</v>
+        <v>6.6276</v>
       </c>
       <c r="V5" t="n">
-        <v>6.2099</v>
+        <v>-1.5061</v>
       </c>
       <c r="W5" t="n">
-        <v>18.1482</v>
+        <v>5.979000000000001</v>
       </c>
       <c r="X5" t="n">
-        <v>-11.9383</v>
+        <v>-7.4851</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. FAYE</t>
+          <t>A. FONT FENOLLAR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>35.9901</v>
+        <v>38.8391</v>
       </c>
       <c r="E6" t="n">
-        <v>30.4941</v>
+        <v>35.4297</v>
       </c>
       <c r="F6" t="n">
-        <v>5.496099999999999</v>
+        <v>3.4098</v>
       </c>
       <c r="G6" t="n">
-        <v>12.1769</v>
+        <v>24.4911</v>
       </c>
       <c r="H6" t="n">
-        <v>14.9078</v>
+        <v>19.7546</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.7309</v>
+        <v>4.736700000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>18.1398</v>
+        <v>48.7706</v>
       </c>
       <c r="K6" t="n">
-        <v>15.7872</v>
+        <v>37.3513</v>
       </c>
       <c r="L6" t="n">
-        <v>2.3531</v>
+        <v>11.4193</v>
       </c>
       <c r="M6" t="n">
-        <v>-5.9636</v>
+        <v>-24.2798</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8791999999999999</v>
+        <v>-17.597</v>
       </c>
       <c r="O6" t="n">
-        <v>-5.0841</v>
+        <v>-6.6831</v>
       </c>
       <c r="P6" t="n">
-        <v>10.0011</v>
+        <v>9.434999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>-8.680199999999999</v>
+        <v>-29.0598</v>
       </c>
       <c r="R6" t="n">
-        <v>18.6813</v>
+        <v>38.4948</v>
       </c>
       <c r="S6" t="n">
-        <v>18.8346</v>
+        <v>2.7321</v>
       </c>
       <c r="T6" t="n">
-        <v>15.488</v>
+        <v>-0.6762000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>3.3469</v>
+        <v>3.4083</v>
       </c>
       <c r="V6" t="n">
-        <v>-5.0222</v>
+        <v>2.181</v>
       </c>
       <c r="W6" t="n">
-        <v>5.5464</v>
+        <v>16.3944</v>
       </c>
       <c r="X6" t="n">
-        <v>-10.5686</v>
+        <v>-14.2134</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. LÓPEZ ÁLVAREZ-TIRADOR</t>
+          <t>V. SANTAMATILDE PERIS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D7" t="n">
-        <v>31.4019</v>
+        <v>31.4261</v>
       </c>
       <c r="E7" t="n">
-        <v>31.4019</v>
+        <v>17.5555</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>13.8703</v>
       </c>
       <c r="G7" t="n">
-        <v>31.4019</v>
+        <v>16.2638</v>
       </c>
       <c r="H7" t="n">
-        <v>9.191800000000001</v>
+        <v>6.386900000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>22.2105</v>
+        <v>9.876799999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>31.4019</v>
+        <v>21.7512</v>
       </c>
       <c r="K7" t="n">
-        <v>9.191800000000001</v>
+        <v>11.3579</v>
       </c>
       <c r="L7" t="n">
-        <v>22.2105</v>
+        <v>10.3935</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-5.4874</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-4.971</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.5167000000000002</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>7.359299999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-9.623699999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>16.983</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>6.199199999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.3534</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.8456</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.6039</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.075</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.4711</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V. SANTAMATILDE PERIS</t>
+          <t>A. LÓPEZ ÁLVAREZ-TIRADOR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>30.3032</v>
+        <v>31.4019</v>
       </c>
       <c r="E8" t="n">
-        <v>16.5797</v>
+        <v>31.4019</v>
       </c>
       <c r="F8" t="n">
-        <v>13.7233</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>16.2638</v>
+        <v>31.4019</v>
       </c>
       <c r="H8" t="n">
-        <v>6.386900000000001</v>
+        <v>9.191800000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>9.876799999999999</v>
+        <v>22.2105</v>
       </c>
       <c r="J8" t="n">
-        <v>21.7512</v>
+        <v>31.4019</v>
       </c>
       <c r="K8" t="n">
-        <v>11.3579</v>
+        <v>9.191800000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>10.3935</v>
+        <v>22.2105</v>
       </c>
       <c r="M8" t="n">
-        <v>-5.4874</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-4.971</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5167000000000002</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>7.359299999999999</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-9.623699999999999</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>16.983</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>5.076300000000001</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.3774</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>3.6988</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.6039</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>3.075</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4711</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. FONT FENOLLAR</t>
+          <t>P. FAYE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>26.8693</v>
+        <v>27.2521</v>
       </c>
       <c r="E9" t="n">
-        <v>25.8742</v>
+        <v>22.2726</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9946999999999999</v>
+        <v>4.979299999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>24.4911</v>
+        <v>12.1769</v>
       </c>
       <c r="H9" t="n">
-        <v>19.7546</v>
+        <v>14.9078</v>
       </c>
       <c r="I9" t="n">
-        <v>4.736700000000001</v>
+        <v>-2.7309</v>
       </c>
       <c r="J9" t="n">
-        <v>48.7706</v>
+        <v>18.1398</v>
       </c>
       <c r="K9" t="n">
-        <v>37.3513</v>
+        <v>15.7872</v>
       </c>
       <c r="L9" t="n">
-        <v>11.4193</v>
+        <v>2.3531</v>
       </c>
       <c r="M9" t="n">
-        <v>-24.2798</v>
+        <v>-5.9636</v>
       </c>
       <c r="N9" t="n">
-        <v>-17.597</v>
+        <v>-0.8791999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>-6.6831</v>
+        <v>-5.0841</v>
       </c>
       <c r="P9" t="n">
-        <v>9.434999999999999</v>
+        <v>10.0011</v>
       </c>
       <c r="Q9" t="n">
-        <v>-29.0598</v>
+        <v>-8.680199999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>38.4948</v>
+        <v>18.6813</v>
       </c>
       <c r="S9" t="n">
-        <v>-9.2379</v>
+        <v>10.0962</v>
       </c>
       <c r="T9" t="n">
-        <v>-10.2314</v>
+        <v>7.2663</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9931999999999999</v>
+        <v>2.83</v>
       </c>
       <c r="V9" t="n">
-        <v>2.181</v>
+        <v>-5.0222</v>
       </c>
       <c r="W9" t="n">
-        <v>16.3944</v>
+        <v>5.5464</v>
       </c>
       <c r="X9" t="n">
-        <v>-14.2134</v>
+        <v>-10.5686</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>14.9913</v>
+        <v>15.0614</v>
       </c>
       <c r="E10" t="n">
-        <v>4.748800000000001</v>
+        <v>4.207600000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>10.2423</v>
+        <v>10.854</v>
       </c>
       <c r="G10" t="n">
         <v>3.826299999999999</v>
@@ -1234,13 +1234,13 @@
         <v>21.3231</v>
       </c>
       <c r="S10" t="n">
-        <v>9.7226</v>
+        <v>9.7927</v>
       </c>
       <c r="T10" t="n">
-        <v>4.0453</v>
+        <v>3.5042</v>
       </c>
       <c r="U10" t="n">
-        <v>5.6772</v>
+        <v>6.2885</v>
       </c>
       <c r="V10" t="n">
         <v>-5.5392</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. LOPEZ VILLENA</t>
+          <t>P. ANTICH MINGUEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>5.773700000000001</v>
+        <v>12.9554</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9042</v>
+        <v>10.4554</v>
       </c>
       <c r="F11" t="n">
-        <v>2.8694</v>
+        <v>2.500399999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>1.6372</v>
+        <v>12.8299</v>
       </c>
       <c r="H11" t="n">
-        <v>2.9293</v>
+        <v>9.897599999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.2921</v>
+        <v>2.932700000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>2.3325</v>
+        <v>46.7782</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9324</v>
+        <v>33.2244</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5999999999999999</v>
+        <v>13.5539</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6952999999999997</v>
+        <v>-33.9481</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.003199999999999981</v>
+        <v>-23.3271</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6922000000000001</v>
+        <v>-10.621</v>
       </c>
       <c r="P11" t="n">
-        <v>1.5096</v>
+        <v>-14.5299</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0757</v>
+        <v>-62.6484</v>
       </c>
       <c r="R11" t="n">
-        <v>3.5853</v>
+        <v>48.1185</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4485</v>
+        <v>7.478899999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.371</v>
+        <v>0.06390000000000026</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.07740000000000002</v>
+        <v>7.4149</v>
       </c>
       <c r="V11" t="n">
-        <v>4.0754</v>
+        <v>7.1765</v>
       </c>
       <c r="W11" t="n">
-        <v>4.0184</v>
+        <v>26.261</v>
       </c>
       <c r="X11" t="n">
-        <v>0.057</v>
+        <v>-19.0845</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>3.723</v>
+        <v>10.5588</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.5184</v>
+        <v>0.2133000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>9.241199999999999</v>
+        <v>10.3455</v>
       </c>
       <c r="G12" t="n">
         <v>6.8035</v>
@@ -1390,13 +1390,13 @@
         <v>20.3796</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.9554</v>
+        <v>1.8803</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.6517</v>
+        <v>1.0803</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3041000000000001</v>
+        <v>0.7999999999999998</v>
       </c>
       <c r="V12" t="n">
         <v>1.6863</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. MARTÍNEZ JURADO</t>
+          <t>M. LOPEZ VILLENA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>3.1189</v>
+        <v>7.5778</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1189</v>
+        <v>4.0734</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>3.5045</v>
       </c>
       <c r="G13" t="n">
-        <v>3.1189</v>
+        <v>1.6372</v>
       </c>
       <c r="H13" t="n">
-        <v>1.268</v>
+        <v>2.9293</v>
       </c>
       <c r="I13" t="n">
-        <v>1.851</v>
+        <v>-1.2921</v>
       </c>
       <c r="J13" t="n">
-        <v>3.1189</v>
+        <v>2.3325</v>
       </c>
       <c r="K13" t="n">
-        <v>1.268</v>
+        <v>2.9324</v>
       </c>
       <c r="L13" t="n">
-        <v>1.851</v>
+        <v>-0.5999999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>-0.6952999999999997</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>-0.003199999999999981</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>-0.6922000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.5096</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-2.0757</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.5853</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>0.3557</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>-0.2018</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>0.5572999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>4.0754</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>4.0184</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. MARTINEZ JURADO</t>
+          <t>D. MARTÍNEZ JURADO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>3.052499999999999</v>
+        <v>3.1189</v>
       </c>
       <c r="E14" t="n">
-        <v>10.7271</v>
+        <v>3.1189</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.6744</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-7.526699999999999</v>
+        <v>3.1189</v>
       </c>
       <c r="H14" t="n">
-        <v>-8.476199999999999</v>
+        <v>1.268</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9495000000000002</v>
+        <v>1.851</v>
       </c>
       <c r="J14" t="n">
-        <v>7.8608</v>
+        <v>3.1189</v>
       </c>
       <c r="K14" t="n">
-        <v>8.8863</v>
+        <v>1.268</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.0253</v>
+        <v>1.851</v>
       </c>
       <c r="M14" t="n">
-        <v>-15.3872</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-17.3625</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.9749</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>4.3401</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-21.1344</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>25.4745</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>13.0688</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>12.0402</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0288</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>-6.829599999999999</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>11.9602</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-18.7899</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>14</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8973</v>
+        <v>2.9794</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3553</v>
+        <v>2.1751</v>
       </c>
       <c r="F15" t="n">
-        <v>0.542</v>
+        <v>0.8043999999999997</v>
       </c>
       <c r="G15" t="n">
         <v>5.018700000000001</v>
@@ -1624,13 +1624,13 @@
         <v>5.0949</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2368999999999999</v>
+        <v>1.319</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.731</v>
+        <v>0.08880000000000002</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9676999999999999</v>
+        <v>1.2302</v>
       </c>
       <c r="V15" t="n">
         <v>-3.7356</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. ANTICH MINGUEZ</t>
+          <t>P. BELLVER VALIENTE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6487000000000003</v>
+        <v>-0.2034</v>
       </c>
       <c r="E16" t="n">
-        <v>2.187</v>
+        <v>-1.3205</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5381</v>
+        <v>1.1171</v>
       </c>
       <c r="G16" t="n">
-        <v>12.8299</v>
+        <v>-0.1057</v>
       </c>
       <c r="H16" t="n">
-        <v>9.897599999999999</v>
+        <v>-1.1731</v>
       </c>
       <c r="I16" t="n">
-        <v>2.932700000000001</v>
+        <v>1.0674</v>
       </c>
       <c r="J16" t="n">
-        <v>46.7782</v>
+        <v>-0.1677999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>33.2244</v>
+        <v>0.259</v>
       </c>
       <c r="L16" t="n">
-        <v>13.5539</v>
+        <v>-0.4268000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-33.9481</v>
+        <v>0.06210000000000004</v>
       </c>
       <c r="N16" t="n">
-        <v>-23.3271</v>
+        <v>-1.4322</v>
       </c>
       <c r="O16" t="n">
-        <v>-10.621</v>
+        <v>1.4942</v>
       </c>
       <c r="P16" t="n">
-        <v>-14.5299</v>
+        <v>0.7548</v>
       </c>
       <c r="Q16" t="n">
-        <v>-62.6484</v>
+        <v>-0.9435</v>
       </c>
       <c r="R16" t="n">
-        <v>48.1185</v>
+        <v>1.6983</v>
       </c>
       <c r="S16" t="n">
-        <v>-4.8281</v>
+        <v>-0.5506</v>
       </c>
       <c r="T16" t="n">
-        <v>-8.2043</v>
+        <v>-0.2093</v>
       </c>
       <c r="U16" t="n">
-        <v>3.3762</v>
+        <v>-0.3415</v>
       </c>
       <c r="V16" t="n">
-        <v>7.1765</v>
+        <v>-0.3018</v>
       </c>
       <c r="W16" t="n">
-        <v>26.261</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-19.0845</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3654000000000002</v>
+        <v>-0.5811999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.03010000000000002</v>
+        <v>-0.7121999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3954999999999997</v>
+        <v>0.131</v>
       </c>
       <c r="G17" t="n">
         <v>-1.4926</v>
@@ -1780,13 +1780,13 @@
         <v>0.1887</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3674</v>
+        <v>0.4208</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7235</v>
+        <v>0.04150000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6438</v>
+        <v>0.3791</v>
       </c>
       <c r="V17" t="n">
         <v>0.3018</v>
@@ -1813,13 +1813,13 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.862</v>
+        <v>-1.0833</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5979</v>
+        <v>-0.7927999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2641</v>
+        <v>-0.2905</v>
       </c>
       <c r="G18" t="n">
         <v>-1.285</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7248</v>
+        <v>0.5035000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4855</v>
+        <v>0.2906</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2393</v>
+        <v>0.2129</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3018</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. BELLVER VALIENTE</t>
+          <t>D. MARTINEZ JURADO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,70 +1888,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0308</v>
+        <v>-2.8133</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6717</v>
+        <v>2.644900000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6409999999999999</v>
+        <v>-5.4581</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1057</v>
+        <v>-7.526699999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1731</v>
+        <v>-8.476199999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0674</v>
+        <v>0.9495000000000002</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1677999999999999</v>
+        <v>7.8608</v>
       </c>
       <c r="K19" t="n">
-        <v>0.259</v>
+        <v>8.8863</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.4268000000000001</v>
+        <v>-1.0253</v>
       </c>
       <c r="M19" t="n">
-        <v>0.06210000000000004</v>
+        <v>-15.3872</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4322</v>
+        <v>-17.3625</v>
       </c>
       <c r="O19" t="n">
-        <v>1.4942</v>
+        <v>1.9749</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7548</v>
+        <v>4.3401</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9435</v>
+        <v>-21.1344</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6983</v>
+        <v>25.4745</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3779</v>
+        <v>7.2029</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5603</v>
+        <v>3.9582</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8177000000000001</v>
+        <v>3.2445</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3018</v>
+        <v>-6.829599999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>11.9602</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3018</v>
+        <v>-18.7899</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>24</v>
       </c>
       <c r="D20" t="n">
-        <v>434.7114999999999</v>
+        <v>456.9564999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>343.3606</v>
+        <v>352.57</v>
       </c>
       <c r="F20" t="n">
-        <v>91.35080000000001</v>
+        <v>104.3875</v>
       </c>
       <c r="G20" t="n">
         <v>235.2111</v>
@@ -1987,7 +1987,7 @@
         <v>91.89319999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>464.6217</v>
+        <v>464.6216999999999</v>
       </c>
       <c r="K20" t="n">
         <v>326.4719</v>
@@ -2005,22 +2005,22 @@
         <v>-46.2589</v>
       </c>
       <c r="P20" t="n">
-        <v>79.254</v>
+        <v>79.25399999999999</v>
       </c>
       <c r="Q20" t="n">
-        <v>-308.5244999999999</v>
+        <v>-308.5245</v>
       </c>
       <c r="R20" t="n">
         <v>387.7785</v>
       </c>
       <c r="S20" t="n">
-        <v>62.95320000000001</v>
+        <v>85.1981</v>
       </c>
       <c r="T20" t="n">
-        <v>22.13359999999999</v>
+        <v>31.3432</v>
       </c>
       <c r="U20" t="n">
-        <v>40.8187</v>
+        <v>53.8538</v>
       </c>
       <c r="V20" t="n">
         <v>57.2938</v>
